--- a/Output Data/Pulse Data/Recover_15.xlsx
+++ b/Output Data/Pulse Data/Recover_15.xlsx
@@ -8,6 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blood Pulse Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blood Pulse Data1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blood Pulse Data2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Blood Pulse Data3" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29265,4 +29268,529 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AA1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
+    <col width="29" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="31" customWidth="1" min="17" max="17"/>
+    <col width="33" customWidth="1" min="19" max="19"/>
+    <col width="38" customWidth="1" min="20" max="20"/>
+    <col width="38" customWidth="1" min="21" max="21"/>
+    <col width="37" customWidth="1" min="22" max="22"/>
+    <col width="32" customWidth="1" min="23" max="23"/>
+    <col width="32" customWidth="1" min="24" max="24"/>
+    <col width="34" customWidth="1" min="25" max="25"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
+    <col width="34" customWidth="1" min="27" max="27"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pulse Number</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Start Time</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>End Time</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Systolic Time From Start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Tidal Wave Time From Systolic</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Dicrotic Time From Tidal Wave</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Tail Wave Time From Dicrotic</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>End Time From Tail Wave</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Systolic Peak Amplitude</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Tidal Wave Peak Ampltiude</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Dicrotic Peak Amplitude</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Tail Wave Peak Ampltitude</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Diastolic Pressure (pF)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Systolic Pressure (pF)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Central Augmentation Index</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Reflection Index</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Stiffens Index (Without Height)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr"/>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Gaussian Systolic Time From Start</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Gaussian Tidal Wave Time From Systolic</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Gaussian Dicrotic Time From Tidal Wave</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Gaussian Tail Wave Time From Dicrotic</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Gaussian End Time From Tail Wave</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Gaussian Systolic Peak Amplitude</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Gaussian Tidal Wave Peak Ampltiude</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Gaussian Dicrotic Peak Amplitude</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Gaussian Tail Wave Peak Ampltitude</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AA1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
+    <col width="29" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="31" customWidth="1" min="17" max="17"/>
+    <col width="33" customWidth="1" min="19" max="19"/>
+    <col width="38" customWidth="1" min="20" max="20"/>
+    <col width="38" customWidth="1" min="21" max="21"/>
+    <col width="37" customWidth="1" min="22" max="22"/>
+    <col width="32" customWidth="1" min="23" max="23"/>
+    <col width="32" customWidth="1" min="24" max="24"/>
+    <col width="34" customWidth="1" min="25" max="25"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
+    <col width="34" customWidth="1" min="27" max="27"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pulse Number</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Start Time</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>End Time</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Systolic Time From Start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Tidal Wave Time From Systolic</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Dicrotic Time From Tidal Wave</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Tail Wave Time From Dicrotic</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>End Time From Tail Wave</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Systolic Peak Amplitude</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Tidal Wave Peak Ampltiude</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Dicrotic Peak Amplitude</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Tail Wave Peak Ampltitude</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Diastolic Pressure (pF)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Systolic Pressure (pF)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Central Augmentation Index</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Reflection Index</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Stiffens Index (Without Height)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr"/>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Gaussian Systolic Time From Start</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Gaussian Tidal Wave Time From Systolic</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Gaussian Dicrotic Time From Tidal Wave</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Gaussian Tail Wave Time From Dicrotic</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Gaussian End Time From Tail Wave</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Gaussian Systolic Peak Amplitude</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Gaussian Tidal Wave Peak Ampltiude</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Gaussian Dicrotic Peak Amplitude</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Gaussian Tail Wave Peak Ampltitude</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AA1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
+    <col width="29" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="31" customWidth="1" min="17" max="17"/>
+    <col width="33" customWidth="1" min="19" max="19"/>
+    <col width="38" customWidth="1" min="20" max="20"/>
+    <col width="38" customWidth="1" min="21" max="21"/>
+    <col width="37" customWidth="1" min="22" max="22"/>
+    <col width="32" customWidth="1" min="23" max="23"/>
+    <col width="32" customWidth="1" min="24" max="24"/>
+    <col width="34" customWidth="1" min="25" max="25"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
+    <col width="34" customWidth="1" min="27" max="27"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pulse Number</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Start Time</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>End Time</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Systolic Time From Start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Tidal Wave Time From Systolic</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Dicrotic Time From Tidal Wave</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Tail Wave Time From Dicrotic</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>End Time From Tail Wave</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Systolic Peak Amplitude</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Tidal Wave Peak Ampltiude</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Dicrotic Peak Amplitude</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Tail Wave Peak Ampltitude</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Diastolic Pressure (pF)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Systolic Pressure (pF)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Central Augmentation Index</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Reflection Index</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Stiffens Index (Without Height)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr"/>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Gaussian Systolic Time From Start</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Gaussian Tidal Wave Time From Systolic</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Gaussian Dicrotic Time From Tidal Wave</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Gaussian Tail Wave Time From Dicrotic</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Gaussian End Time From Tail Wave</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Gaussian Systolic Peak Amplitude</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Gaussian Tidal Wave Peak Ampltiude</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Gaussian Dicrotic Peak Amplitude</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Gaussian Tail Wave Peak Ampltitude</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>